--- a/booking_forms/026_hotel_booking_appointment_form--booking_forms.xlsx
+++ b/booking_forms/026_hotel_booking_appointment_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -824,8 +824,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -853,12 +853,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'single',_'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'single', 'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'double',_'label':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'double', 'label': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'suite',_'label':_'suite'}</t>
+          <t>suite</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'suite', 'label': 'Suite'}</t>
+          <t>Suite</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'wi-fi',_'label':_'wi-fi'}</t>
+          <t>wi-fi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Wi-Fi', 'label': 'Wi-Fi'}</t>
+          <t>Wi-Fi</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'mini-bar',_'label':_'mini-bar'}</t>
+          <t>mini-bar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Mini-Bar', 'label': 'Mini-Bar'}</t>
+          <t>Mini-Bar</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'gym',_'label':_'gym'}</t>
+          <t>gym</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Gym', 'label': 'Gym'}</t>
+          <t>Gym</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
